--- a/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0001T0006Z000C1N46_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0001T0006Z000C1N46_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>92.61800479305364</v>
+        <v>15.05042577887122</v>
       </c>
       <c r="D2" t="n">
-        <v>92.71322451136497</v>
+        <v>15.06589898309681</v>
       </c>
       <c r="E2" t="n">
-        <v>17.93984240567724</v>
+        <v>2.915224390922552</v>
       </c>
       <c r="F2" t="n">
-        <v>18.29857800629237</v>
+        <v>2.97351892602251</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>36.83049741712785</v>
+        <v>5.984955830283276</v>
       </c>
       <c r="D3" t="n">
-        <v>35.53652725165391</v>
+        <v>5.774685678393761</v>
       </c>
       <c r="E3" t="n">
-        <v>17.93984240567724</v>
+        <v>2.915224390922552</v>
       </c>
       <c r="F3" t="n">
-        <v>18.29857800629237</v>
+        <v>2.97351892602251</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>36.21539215812118</v>
+        <v>5.885001225694692</v>
       </c>
       <c r="D4" t="n">
-        <v>36.22199182810477</v>
+        <v>5.886073672067026</v>
       </c>
       <c r="E4" t="n">
-        <v>17.93984240567724</v>
+        <v>2.915224390922552</v>
       </c>
       <c r="F4" t="n">
-        <v>18.29857800629237</v>
+        <v>2.97351892602251</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>44.41207796961014</v>
+        <v>7.216962670061648</v>
       </c>
       <c r="D5" t="n">
-        <v>44.88198229207948</v>
+        <v>7.293322122462916</v>
       </c>
       <c r="E5" t="n">
-        <v>17.93984240567724</v>
+        <v>2.915224390922552</v>
       </c>
       <c r="F5" t="n">
-        <v>18.29857800629237</v>
+        <v>2.97351892602251</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>50.8517620836415</v>
+        <v>8.263411338591743</v>
       </c>
       <c r="D6" t="n">
-        <v>51.53963828801515</v>
+        <v>8.375191221802462</v>
       </c>
       <c r="E6" t="n">
-        <v>17.93984240567724</v>
+        <v>2.915224390922552</v>
       </c>
       <c r="F6" t="n">
-        <v>18.29857800629237</v>
+        <v>2.97351892602251</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>41.63737743448443</v>
+        <v>6.766073833103721</v>
       </c>
       <c r="D7" t="n">
-        <v>39.89438876305829</v>
+        <v>6.482838173996972</v>
       </c>
       <c r="E7" t="n">
-        <v>17.93984240567724</v>
+        <v>2.915224390922552</v>
       </c>
       <c r="F7" t="n">
-        <v>18.29857800629237</v>
+        <v>2.97351892602251</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>58.7570669809758</v>
+        <v>9.548023384408568</v>
       </c>
       <c r="D8" t="n">
-        <v>60.08128098118517</v>
+        <v>9.763208159442591</v>
       </c>
       <c r="E8" t="n">
-        <v>17.93984240567724</v>
+        <v>2.915224390922552</v>
       </c>
       <c r="F8" t="n">
-        <v>18.29857800629237</v>
+        <v>2.97351892602251</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>46.91668207158889</v>
+        <v>7.623960836633194</v>
       </c>
       <c r="D9" t="n">
-        <v>45.58030719984016</v>
+        <v>7.406799919974027</v>
       </c>
       <c r="E9" t="n">
-        <v>17.93984240567724</v>
+        <v>2.915224390922552</v>
       </c>
       <c r="F9" t="n">
-        <v>18.29857800629237</v>
+        <v>2.97351892602251</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>29.27376604835804</v>
+        <v>4.756986982858181</v>
       </c>
       <c r="D10" t="n">
-        <v>28.16126991826976</v>
+        <v>4.576206361718837</v>
       </c>
       <c r="E10" t="n">
-        <v>17.93984240567724</v>
+        <v>2.915224390922552</v>
       </c>
       <c r="F10" t="n">
-        <v>18.29857800629237</v>
+        <v>2.97351892602251</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>20.80351774074541</v>
+        <v>3.380571632871129</v>
       </c>
       <c r="D11" t="n">
-        <v>20.29442856702074</v>
+        <v>3.297844642140871</v>
       </c>
       <c r="E11" t="n">
-        <v>17.93984240567724</v>
+        <v>2.915224390922552</v>
       </c>
       <c r="F11" t="n">
-        <v>18.29857800629237</v>
+        <v>2.97351892602251</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>37.43210343511236</v>
+        <v>6.082716808205759</v>
       </c>
       <c r="D12" t="n">
-        <v>37.93303851350421</v>
+        <v>6.164118758444434</v>
       </c>
       <c r="E12" t="n">
-        <v>17.93984240567724</v>
+        <v>2.915224390922552</v>
       </c>
       <c r="F12" t="n">
-        <v>18.29857800629237</v>
+        <v>2.97351892602251</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
